--- a/experiments/s_f_sbm_results/sbm_min_600_chants_f_reduct_50_20_iter/colour_between_partitions_edges.xlsx
+++ b/experiments/s_f_sbm_results/sbm_min_600_chants_f_reduct_50_20_iter/colour_between_partitions_edges.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\watticka\network_analysis\project\ChantNets\experiments\visual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annad\Documents\MFFuck\Erasmus\subjects\Network_analysis\project\ChantNets\experiments\s_f_sbm_results\sbm_min_600_chants_f_reduct_50_20_iter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BFAE80-B792-47F0-8120-82A62C726FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FDD513-BAE0-4AEA-8A70-AC10C5422143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -641,52 +641,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -789,6 +743,52 @@
           <color indexed="64"/>
         </left>
         <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1264,50 +1264,53 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE0E619F-52AC-41B4-BEE3-91236F27EFDD}" name="dc_sbm_between_edges" displayName="dc_sbm_between_edges" ref="B2:Q19" tableType="queryTable" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE0E619F-52AC-41B4-BEE3-91236F27EFDD}" name="dc_sbm_between_edges" displayName="dc_sbm_between_edges" ref="B2:Q19" tableType="queryTable" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{2F102C56-E8A2-4AF8-977E-CF014F572AE8}" uniqueName="1" name="s_part" queryTableFieldId="1" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{B7945E95-43C0-4C73-A628-47B8A76C50C0}" uniqueName="2" name="n_edges" queryTableFieldId="2" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{CC1B4593-E926-43E6-9874-63644023BB8A}" uniqueName="3" name="f_part_721" queryTableFieldId="3" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{96ADD317-F8F4-43C7-AB30-0F0DC43B30ED}" uniqueName="4" name="f_part_439" queryTableFieldId="4" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{D6DC3CDD-98B0-49CB-B425-C580A8845C2A}" uniqueName="5" name="f_part_650" queryTableFieldId="5" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{C07EC01A-9E6B-4004-9196-3CC0805513AE}" uniqueName="6" name="f_part_545" queryTableFieldId="6" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{4BF11679-E5E5-4699-A841-5B962E477FE5}" uniqueName="7" name="f_part_975" queryTableFieldId="7" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{B421561F-76F1-43E6-AAAF-F719E5C80758}" uniqueName="8" name="f_part_611" queryTableFieldId="8" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{D85CFE2D-9996-47B5-8872-19C5BC77ADC9}" uniqueName="9" name="f_part_1043" queryTableFieldId="9" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{07C4527F-C4B9-442E-93A7-2516C7AC965A}" uniqueName="10" name="f_part_843" queryTableFieldId="10" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{79CB7AD6-C5AF-4697-8DD1-55AD4109A5E5}" uniqueName="11" name="f_part_651" queryTableFieldId="11" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{FD202B59-4004-467A-B894-D8A0AF98F3F0}" uniqueName="12" name="f_part_564" queryTableFieldId="12" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{AD2724FD-F1B9-4BB1-AE5E-56C5AD87A78E}" uniqueName="13" name="f_part_579" queryTableFieldId="13" dataDxfId="25"/>
-    <tableColumn id="14" xr3:uid="{432CB750-9707-432C-9AF5-EA079AC38CC8}" uniqueName="14" name="f_part_752" queryTableFieldId="14" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{209AFC51-5D2F-421D-8C64-C86C6780A695}" uniqueName="15" name="f_part_371" queryTableFieldId="15" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{2D04C048-996C-4D19-A85E-E93FA533A498}" uniqueName="16" name="f_part_370" queryTableFieldId="16" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{2F102C56-E8A2-4AF8-977E-CF014F572AE8}" uniqueName="1" name="s_part" queryTableFieldId="1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{B7945E95-43C0-4C73-A628-47B8A76C50C0}" uniqueName="2" name="n_edges" queryTableFieldId="2" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{CC1B4593-E926-43E6-9874-63644023BB8A}" uniqueName="3" name="f_part_721" queryTableFieldId="3" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{96ADD317-F8F4-43C7-AB30-0F0DC43B30ED}" uniqueName="4" name="f_part_439" queryTableFieldId="4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{D6DC3CDD-98B0-49CB-B425-C580A8845C2A}" uniqueName="5" name="f_part_650" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{C07EC01A-9E6B-4004-9196-3CC0805513AE}" uniqueName="6" name="f_part_545" queryTableFieldId="6" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{4BF11679-E5E5-4699-A841-5B962E477FE5}" uniqueName="7" name="f_part_975" queryTableFieldId="7" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{B421561F-76F1-43E6-AAAF-F719E5C80758}" uniqueName="8" name="f_part_611" queryTableFieldId="8" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{D85CFE2D-9996-47B5-8872-19C5BC77ADC9}" uniqueName="9" name="f_part_1043" queryTableFieldId="9" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{07C4527F-C4B9-442E-93A7-2516C7AC965A}" uniqueName="10" name="f_part_843" queryTableFieldId="10" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{79CB7AD6-C5AF-4697-8DD1-55AD4109A5E5}" uniqueName="11" name="f_part_651" queryTableFieldId="11" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{FD202B59-4004-467A-B894-D8A0AF98F3F0}" uniqueName="12" name="f_part_564" queryTableFieldId="12" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{AD2724FD-F1B9-4BB1-AE5E-56C5AD87A78E}" uniqueName="13" name="f_part_579" queryTableFieldId="13" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{432CB750-9707-432C-9AF5-EA079AC38CC8}" uniqueName="14" name="f_part_752" queryTableFieldId="14" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{209AFC51-5D2F-421D-8C64-C86C6780A695}" uniqueName="15" name="f_part_371" queryTableFieldId="15" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{2D04C048-996C-4D19-A85E-E93FA533A498}" uniqueName="16" name="f_part_370" queryTableFieldId="16" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{246D5E9F-A934-4177-873D-61ECA6C14CEF}" name="dc_sbm_weighted_between_edges" displayName="dc_sbm_weighted_between_edges" ref="B2:S21" tableType="queryTable" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{246D5E9F-A934-4177-873D-61ECA6C14CEF}" name="dc_sbm_weighted_between_edges" displayName="dc_sbm_weighted_between_edges" ref="B2:S21" tableType="queryTable" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:S21">
+    <sortCondition ref="E3:E21"/>
+  </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{FDA7F15C-B2EF-4583-AE57-58382633F285}" uniqueName="1" name="s_part" queryTableFieldId="1" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{EE491942-4C32-4423-8E18-FD0088BE84EF}" uniqueName="2" name="n_edges" queryTableFieldId="2" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{DF242A31-263A-4604-A2AF-2A20300B3E4E}" uniqueName="3" name="f_part_385" queryTableFieldId="3" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{8087C44E-9AEC-4ADB-B7A4-9EF4826463A4}" uniqueName="4" name="f_part_540" queryTableFieldId="4" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{6BFC048A-1747-4880-8F68-0286C17387BE}" uniqueName="5" name="f_part_677" queryTableFieldId="5" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{DB7A03EF-09E3-42E5-B379-318F7F7C9012}" uniqueName="6" name="f_part_369" queryTableFieldId="6" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{273440A6-E600-40D6-9CF0-22DDD133BDAA}" uniqueName="7" name="f_part_819" queryTableFieldId="7" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{9F58F552-1CAF-49DF-8A69-942F7668ECA5}" uniqueName="8" name="f_part_684" queryTableFieldId="8" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{FBD6BF0D-27A7-4ACC-90EF-FB30905A6F4B}" uniqueName="9" name="f_part_461" queryTableFieldId="9" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{FC07790F-428E-4D85-943D-CD17FE0C5292}" uniqueName="10" name="f_part_977" queryTableFieldId="10" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{1AFF6571-2DBE-4E9E-95F5-5D79D315556A}" uniqueName="11" name="f_part_544" queryTableFieldId="11" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{EAB45EB4-75A0-4716-98AD-0D8BC1758596}" uniqueName="12" name="f_part_701" queryTableFieldId="12" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{7FAAFF46-5335-4E43-93F9-FA37270C82C7}" uniqueName="13" name="f_part_558" queryTableFieldId="13" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{AF5163B1-3DF2-46B6-AFA1-5924E906BDA9}" uniqueName="14" name="f_part_897" queryTableFieldId="14" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{51CE3B18-607D-44C0-B07B-3E0831A23A50}" uniqueName="15" name="f_part_938" queryTableFieldId="15" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{E6D413EC-42A5-4CA6-8804-55E9E02B2194}" uniqueName="16" name="f_part_1031" queryTableFieldId="16" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{8A6C2AC3-DC6B-4EC4-BA5F-A16A106C3F69}" uniqueName="17" name="f_part_936" queryTableFieldId="17" dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{330D6798-37E3-4D00-96A3-7A5A7405F3D8}" uniqueName="18" name="f_part_761" queryTableFieldId="18" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{FDA7F15C-B2EF-4583-AE57-58382633F285}" uniqueName="1" name="s_part" queryTableFieldId="1" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{EE491942-4C32-4423-8E18-FD0088BE84EF}" uniqueName="2" name="n_edges" queryTableFieldId="2" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{DF242A31-263A-4604-A2AF-2A20300B3E4E}" uniqueName="3" name="f_part_385" queryTableFieldId="3" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{8087C44E-9AEC-4ADB-B7A4-9EF4826463A4}" uniqueName="4" name="f_part_540" queryTableFieldId="4" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{6BFC048A-1747-4880-8F68-0286C17387BE}" uniqueName="5" name="f_part_677" queryTableFieldId="5" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{DB7A03EF-09E3-42E5-B379-318F7F7C9012}" uniqueName="6" name="f_part_369" queryTableFieldId="6" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{273440A6-E600-40D6-9CF0-22DDD133BDAA}" uniqueName="7" name="f_part_819" queryTableFieldId="7" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{9F58F552-1CAF-49DF-8A69-942F7668ECA5}" uniqueName="8" name="f_part_684" queryTableFieldId="8" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{FBD6BF0D-27A7-4ACC-90EF-FB30905A6F4B}" uniqueName="9" name="f_part_461" queryTableFieldId="9" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{FC07790F-428E-4D85-943D-CD17FE0C5292}" uniqueName="10" name="f_part_977" queryTableFieldId="10" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{1AFF6571-2DBE-4E9E-95F5-5D79D315556A}" uniqueName="11" name="f_part_544" queryTableFieldId="11" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{EAB45EB4-75A0-4716-98AD-0D8BC1758596}" uniqueName="12" name="f_part_701" queryTableFieldId="12" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{7FAAFF46-5335-4E43-93F9-FA37270C82C7}" uniqueName="13" name="f_part_558" queryTableFieldId="13" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{AF5163B1-3DF2-46B6-AFA1-5924E906BDA9}" uniqueName="14" name="f_part_897" queryTableFieldId="14" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{51CE3B18-607D-44C0-B07B-3E0831A23A50}" uniqueName="15" name="f_part_938" queryTableFieldId="15" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{E6D413EC-42A5-4CA6-8804-55E9E02B2194}" uniqueName="16" name="f_part_1031" queryTableFieldId="16" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{8A6C2AC3-DC6B-4EC4-BA5F-A16A106C3F69}" uniqueName="17" name="f_part_936" queryTableFieldId="17" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{330D6798-37E3-4D00-96A3-7A5A7405F3D8}" uniqueName="18" name="f_part_761" queryTableFieldId="18" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2588,46 +2591,46 @@
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B3" s="4">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="C3" s="5">
-        <v>2832</v>
+        <v>1185</v>
       </c>
       <c r="D3" s="9">
-        <v>5.1906779661016901E-2</v>
+        <v>5.0632911392405E-2</v>
       </c>
       <c r="E3" s="9">
-        <v>0.23764124293785299</v>
+        <v>0</v>
       </c>
       <c r="F3" s="9">
-        <v>0.19209039548022599</v>
+        <v>3.0379746835442999E-2</v>
       </c>
       <c r="G3" s="9">
-        <v>0.114053672316384</v>
+        <v>0</v>
       </c>
       <c r="H3" s="9">
-        <v>1.02401129943502E-2</v>
+        <v>0.25485232067510499</v>
       </c>
       <c r="I3" s="9">
-        <v>9.63983050847457E-2</v>
+        <v>1.8565400843881801E-2</v>
       </c>
       <c r="J3" s="9">
-        <v>6.0028248587570597E-3</v>
+        <v>0.18649789029535799</v>
       </c>
       <c r="K3" s="9">
         <v>0</v>
       </c>
       <c r="L3" s="9">
-        <v>2.4717514124293701E-3</v>
+        <v>3.7974683544303799E-2</v>
       </c>
       <c r="M3" s="9">
-        <v>0</v>
+        <v>5.9071729957805904E-3</v>
       </c>
       <c r="N3" s="9">
-        <v>0.27048022598869997</v>
+        <v>0</v>
       </c>
       <c r="O3" s="9">
-        <v>6.70903954802259E-3</v>
+        <v>3.0379746835442999E-2</v>
       </c>
       <c r="P3" s="9">
         <v>0</v>
@@ -2636,110 +2639,110 @@
         <v>0</v>
       </c>
       <c r="R3" s="9">
-        <v>1.20056497175141E-2</v>
+        <v>0.119831223628691</v>
       </c>
       <c r="S3" s="10">
-        <v>0</v>
+        <v>0.264978902953586</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="C4" s="5">
-        <v>1567</v>
+        <v>115</v>
       </c>
       <c r="D4" s="9">
-        <v>4.7223994894703199E-2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="9">
-        <v>1.7868538608806599E-2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="9">
-        <v>4.4671346522016497E-3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="9">
         <v>0</v>
       </c>
       <c r="H4" s="9">
-        <v>0.216975111678366</v>
+        <v>0</v>
       </c>
       <c r="I4" s="9">
-        <v>4.0842373962986601E-2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="9">
-        <v>0.153158902361199</v>
+        <v>0</v>
       </c>
       <c r="K4" s="9">
         <v>0</v>
       </c>
       <c r="L4" s="9">
-        <v>0.10338225909380901</v>
+        <v>0</v>
       </c>
       <c r="M4" s="9">
-        <v>5.10529674537332E-3</v>
+        <v>0</v>
       </c>
       <c r="N4" s="9">
         <v>0</v>
       </c>
       <c r="O4" s="9">
-        <v>0.292916400765794</v>
+        <v>0</v>
       </c>
       <c r="P4" s="9">
         <v>0</v>
       </c>
-      <c r="Q4" s="9">
-        <v>0</v>
+      <c r="Q4" s="12">
+        <v>1</v>
       </c>
       <c r="R4" s="9">
-        <v>2.6164645820038201E-2</v>
+        <v>0</v>
       </c>
       <c r="S4" s="10">
-        <v>9.1895341416719803E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C5" s="5">
-        <v>2854</v>
+        <v>1606</v>
       </c>
       <c r="D5" s="9">
-        <v>5.0105115627189903E-2</v>
+        <v>4.4209215442092102E-2</v>
       </c>
       <c r="E5" s="9">
-        <v>9.2151366503153406E-2</v>
+        <v>3.1133250311332502E-3</v>
       </c>
       <c r="F5" s="9">
-        <v>8.0238262088297096E-2</v>
+        <v>1.2453300124532999E-3</v>
       </c>
       <c r="G5" s="9">
-        <v>3.9593552908198999E-2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="9">
-        <v>0.154519971969166</v>
+        <v>0.13200498132004901</v>
       </c>
       <c r="I5" s="9">
-        <v>5.7813594954449897E-2</v>
+        <v>8.7173100871730993E-3</v>
       </c>
       <c r="J5" s="9">
-        <v>7.6734407848633501E-2</v>
+        <v>0.13885429638854199</v>
       </c>
       <c r="K5" s="9">
-        <v>3.1534688156972602E-3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="9">
-        <v>8.61948142957253E-2</v>
+        <v>0.231631382316313</v>
       </c>
       <c r="M5" s="9">
-        <v>2.3826208829712599E-2</v>
+        <v>9.5890410958904104E-2</v>
       </c>
       <c r="N5" s="9">
-        <v>0.11737911702873099</v>
+        <v>6.2266500622664995E-4</v>
       </c>
       <c r="O5" s="9">
-        <v>9.1100210231254294E-2</v>
+        <v>1.86799501867995E-2</v>
       </c>
       <c r="P5" s="9">
         <v>0</v>
@@ -2748,110 +2751,110 @@
         <v>0</v>
       </c>
       <c r="R5" s="9">
-        <v>6.4470918009810793E-2</v>
+        <v>0.123910336239103</v>
       </c>
       <c r="S5" s="10">
-        <v>6.2718990889978898E-2</v>
+        <v>0.201120797011207</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="C6" s="5">
-        <v>7226</v>
+        <v>1222</v>
       </c>
       <c r="D6" s="9">
-        <v>5.0096872405203399E-2</v>
+        <v>0.14484451718494201</v>
       </c>
       <c r="E6" s="9">
-        <v>0.128563520619983</v>
+        <v>4.90998363338788E-3</v>
       </c>
       <c r="F6" s="9">
-        <v>8.2895101024079695E-2</v>
+        <v>2.6186579378068699E-2</v>
       </c>
       <c r="G6" s="9">
-        <v>5.88153888735123E-2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9">
-        <v>3.8748962081372802E-2</v>
+        <v>0.23404255319148901</v>
       </c>
       <c r="I6" s="9">
-        <v>6.5042900636590004E-2</v>
+        <v>0.15711947626841199</v>
       </c>
       <c r="J6" s="9">
-        <v>9.6180459451978895E-2</v>
+        <v>0.25941080196399302</v>
       </c>
       <c r="K6" s="9">
-        <v>1.6606698034873999E-3</v>
+        <v>2.6186579378068699E-2</v>
       </c>
       <c r="L6" s="9">
-        <v>0.111264876833656</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9">
-        <v>1.12095211735399E-2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="9">
-        <v>0.167174093551065</v>
+        <v>0</v>
       </c>
       <c r="O6" s="9">
-        <v>1.28701909770274E-2</v>
+        <v>7.9378068739770796E-2</v>
       </c>
       <c r="P6" s="9">
-        <v>0</v>
+        <v>1.55482815057283E-2</v>
       </c>
       <c r="Q6" s="9">
         <v>0</v>
       </c>
       <c r="R6" s="9">
-        <v>6.9748131746471001E-2</v>
+        <v>4.9918166939443502E-2</v>
       </c>
       <c r="S6" s="10">
-        <v>0.10572931082203101</v>
+        <v>2.45499181669394E-3</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
-        <v>127</v>
+        <v>254</v>
       </c>
       <c r="C7" s="5">
-        <v>1185</v>
+        <v>1567</v>
       </c>
       <c r="D7" s="9">
-        <v>5.0632911392405E-2</v>
+        <v>4.7223994894703199E-2</v>
       </c>
       <c r="E7" s="9">
-        <v>0</v>
+        <v>1.7868538608806599E-2</v>
       </c>
       <c r="F7" s="9">
-        <v>3.0379746835442999E-2</v>
+        <v>4.4671346522016497E-3</v>
       </c>
       <c r="G7" s="9">
         <v>0</v>
       </c>
       <c r="H7" s="9">
-        <v>0.25485232067510499</v>
+        <v>0.216975111678366</v>
       </c>
       <c r="I7" s="9">
-        <v>1.8565400843881801E-2</v>
+        <v>4.0842373962986601E-2</v>
       </c>
       <c r="J7" s="9">
-        <v>0.18649789029535799</v>
+        <v>0.153158902361199</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
       </c>
       <c r="L7" s="9">
-        <v>3.7974683544303799E-2</v>
+        <v>0.10338225909380901</v>
       </c>
       <c r="M7" s="9">
-        <v>5.9071729957805904E-3</v>
+        <v>5.10529674537332E-3</v>
       </c>
       <c r="N7" s="9">
         <v>0</v>
       </c>
       <c r="O7" s="9">
-        <v>3.0379746835442999E-2</v>
+        <v>0.292916400765794</v>
       </c>
       <c r="P7" s="9">
         <v>0</v>
@@ -2860,110 +2863,110 @@
         <v>0</v>
       </c>
       <c r="R7" s="9">
-        <v>0.119831223628691</v>
+        <v>2.6164645820038201E-2</v>
       </c>
       <c r="S7" s="10">
-        <v>0.264978902953586</v>
+        <v>9.1895341416719803E-2</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="C8" s="5">
-        <v>4419</v>
+        <v>987</v>
       </c>
       <c r="D8" s="9">
-        <v>5.2274270196877103E-2</v>
+        <v>7.3961499493414296E-2</v>
       </c>
       <c r="E8" s="9">
-        <v>0.10545372256166501</v>
+        <v>8.5106382978723402E-2</v>
       </c>
       <c r="F8" s="9">
-        <v>8.3729350531794505E-2</v>
+        <v>2.0263424518743599E-2</v>
       </c>
       <c r="G8" s="9">
-        <v>3.6433582258429499E-2</v>
+        <v>1.1144883485309001E-2</v>
       </c>
       <c r="H8" s="9">
-        <v>0.104548540393754</v>
+        <v>6.7882472137791194E-2</v>
       </c>
       <c r="I8" s="9">
-        <v>6.0647205250056499E-2</v>
+        <v>6.28166160081053E-2</v>
       </c>
       <c r="J8" s="9">
-        <v>9.4365241004752201E-2</v>
+        <v>9.1185410334346503E-2</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
       </c>
       <c r="L8" s="9">
-        <v>0.104548540393754</v>
+        <v>8.6119554204660498E-2</v>
       </c>
       <c r="M8" s="9">
-        <v>4.2090970807875001E-2</v>
+        <v>3.0395136778115501E-3</v>
       </c>
       <c r="N8" s="9">
-        <v>0.12763068567549199</v>
+        <v>6.9908814589665594E-2</v>
       </c>
       <c r="O8" s="9">
-        <v>1.49355057705363E-2</v>
+        <v>5.8763931104356598E-2</v>
       </c>
       <c r="P8" s="9">
-        <v>0</v>
+        <v>0.17730496453900699</v>
       </c>
       <c r="Q8" s="9">
         <v>0</v>
       </c>
       <c r="R8" s="9">
-        <v>7.3093460058836796E-2</v>
+        <v>2.73556231003039E-2</v>
       </c>
       <c r="S8" s="10">
-        <v>0.100248925096175</v>
+        <v>0.16514690982776001</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="C9" s="5">
-        <v>2164</v>
+        <v>2854</v>
       </c>
       <c r="D9" s="9">
-        <v>4.0203327171903801E-2</v>
+        <v>5.0105115627189903E-2</v>
       </c>
       <c r="E9" s="9">
-        <v>0.190388170055452</v>
+        <v>9.2151366503153406E-2</v>
       </c>
       <c r="F9" s="9">
-        <v>0.134011090573012</v>
+        <v>8.0238262088297096E-2</v>
       </c>
       <c r="G9" s="9">
-        <v>7.8096118299445405E-2</v>
+        <v>3.9593552908198999E-2</v>
       </c>
       <c r="H9" s="9">
-        <v>1.4325323475046199E-2</v>
+        <v>0.154519971969166</v>
       </c>
       <c r="I9" s="9">
-        <v>6.3308687615526799E-2</v>
+        <v>5.7813594954449897E-2</v>
       </c>
       <c r="J9" s="9">
-        <v>2.2643253234750398E-2</v>
+        <v>7.6734407848633501E-2</v>
       </c>
       <c r="K9" s="9">
-        <v>0</v>
+        <v>3.1534688156972602E-3</v>
       </c>
       <c r="L9" s="9">
-        <v>0.125693160813308</v>
+        <v>8.61948142957253E-2</v>
       </c>
       <c r="M9" s="9">
-        <v>5.9611829944547098E-2</v>
+        <v>2.3826208829712599E-2</v>
       </c>
       <c r="N9" s="9">
-        <v>0.248613678373382</v>
+        <v>0.11737911702873099</v>
       </c>
       <c r="O9" s="9">
-        <v>4.6210720887245801E-3</v>
+        <v>9.1100210231254294E-2</v>
       </c>
       <c r="P9" s="9">
         <v>0</v>
@@ -2972,54 +2975,54 @@
         <v>0</v>
       </c>
       <c r="R9" s="9">
-        <v>1.8022181146025801E-2</v>
+        <v>6.4470918009810793E-2</v>
       </c>
       <c r="S9" s="10">
-        <v>4.6210720887245802E-4</v>
+        <v>6.2718990889978898E-2</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
-        <v>169</v>
+        <v>97</v>
       </c>
       <c r="C10" s="5">
-        <v>744</v>
+        <v>4419</v>
       </c>
       <c r="D10" s="9">
-        <v>1.6129032258064498E-2</v>
+        <v>5.2274270196877103E-2</v>
       </c>
       <c r="E10" s="9">
-        <v>0.146505376344086</v>
+        <v>0.10545372256166501</v>
       </c>
       <c r="F10" s="9">
-        <v>8.3333333333333301E-2</v>
+        <v>8.3729350531794505E-2</v>
       </c>
       <c r="G10" s="9">
-        <v>4.9731182795698901E-2</v>
+        <v>3.6433582258429499E-2</v>
       </c>
       <c r="H10" s="9">
-        <v>3.36021505376344E-2</v>
+        <v>0.104548540393754</v>
       </c>
       <c r="I10" s="9">
-        <v>3.36021505376344E-2</v>
+        <v>6.0647205250056499E-2</v>
       </c>
       <c r="J10" s="9">
-        <v>3.2258064516128997E-2</v>
+        <v>9.4365241004752201E-2</v>
       </c>
       <c r="K10" s="9">
-        <v>2.6881720430107499E-3</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9">
-        <v>0.135752688172043</v>
+        <v>0.104548540393754</v>
       </c>
       <c r="M10" s="9">
-        <v>6.0483870967741903E-2</v>
+        <v>4.2090970807875001E-2</v>
       </c>
       <c r="N10" s="9">
-        <v>0.204301075268817</v>
+        <v>0.12763068567549199</v>
       </c>
       <c r="O10" s="9">
-        <v>6.7204301075268801E-3</v>
+        <v>1.49355057705363E-2</v>
       </c>
       <c r="P10" s="9">
         <v>0</v>
@@ -3028,166 +3031,166 @@
         <v>0</v>
       </c>
       <c r="R10" s="9">
-        <v>5.1075268817204297E-2</v>
+        <v>7.3093460058836796E-2</v>
       </c>
       <c r="S10" s="10">
-        <v>0.143817204301075</v>
+        <v>0.100248925096175</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
-        <v>181</v>
+        <v>328</v>
       </c>
       <c r="C11" s="5">
-        <v>1222</v>
+        <v>10918</v>
       </c>
       <c r="D11" s="9">
-        <v>0.14484451718494201</v>
+        <v>4.4696830921414098E-2</v>
       </c>
       <c r="E11" s="9">
-        <v>4.90998363338788E-3</v>
+        <v>0.11311595530316899</v>
       </c>
       <c r="F11" s="9">
-        <v>2.6186579378068699E-2</v>
+        <v>6.6862062648836698E-3</v>
       </c>
       <c r="G11" s="9">
-        <v>0</v>
+        <v>3.0225315991939902E-3</v>
       </c>
       <c r="H11" s="9">
-        <v>0.23404255319148901</v>
+        <v>0.123282652500457</v>
       </c>
       <c r="I11" s="9">
-        <v>0.15711947626841199</v>
+        <v>7.2907125847224696E-2</v>
       </c>
       <c r="J11" s="9">
-        <v>0.25941080196399302</v>
+        <v>0.10249129877266799</v>
       </c>
       <c r="K11" s="9">
-        <v>2.6186579378068699E-2</v>
+        <v>9.1591866642242099E-4</v>
       </c>
       <c r="L11" s="9">
-        <v>0</v>
+        <v>9.9560359040117202E-2</v>
       </c>
       <c r="M11" s="9">
-        <v>0</v>
+        <v>1.5570617329181101E-3</v>
       </c>
       <c r="N11" s="9">
-        <v>0</v>
+        <v>0.139860780362703</v>
       </c>
       <c r="O11" s="9">
-        <v>7.9378068739770796E-2</v>
+        <v>0.20324235207913499</v>
       </c>
       <c r="P11" s="9">
-        <v>1.55482815057283E-2</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="9">
         <v>0</v>
       </c>
       <c r="R11" s="9">
-        <v>4.9918166939443502E-2</v>
+        <v>2.4729803993405299E-3</v>
       </c>
       <c r="S11" s="10">
-        <v>2.45499181669394E-3</v>
+        <v>8.6187946510349805E-2</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="C12" s="5">
-        <v>987</v>
+        <v>9523</v>
       </c>
       <c r="D12" s="9">
-        <v>7.3961499493414296E-2</v>
+        <v>1.0500892575868901E-2</v>
       </c>
       <c r="E12" s="9">
-        <v>8.5106382978723402E-2</v>
+        <v>0.12716580909377201</v>
       </c>
       <c r="F12" s="9">
-        <v>2.0263424518743599E-2</v>
+        <v>4.20035703034757E-3</v>
       </c>
       <c r="G12" s="9">
-        <v>1.1144883485309001E-2</v>
+        <v>5.9855087682453003E-3</v>
       </c>
       <c r="H12" s="9">
-        <v>6.7882472137791194E-2</v>
+        <v>2.3942035072981201E-2</v>
       </c>
       <c r="I12" s="9">
-        <v>6.28166160081053E-2</v>
+        <v>7.5291399768980305E-2</v>
       </c>
       <c r="J12" s="9">
-        <v>9.1185410334346503E-2</v>
+        <v>0.103223774020791</v>
       </c>
       <c r="K12" s="9">
-        <v>0</v>
+        <v>4.2003570303475701E-4</v>
       </c>
       <c r="L12" s="9">
-        <v>8.6119554204660498E-2</v>
+        <v>0.113934684448178</v>
       </c>
       <c r="M12" s="9">
-        <v>3.0395136778115501E-3</v>
+        <v>3.1502677727606799E-4</v>
       </c>
       <c r="N12" s="9">
-        <v>6.9908814589665594E-2</v>
+        <v>0.17515488816549399</v>
       </c>
       <c r="O12" s="9">
-        <v>5.8763931104356598E-2</v>
+        <v>0.24225559172529601</v>
       </c>
       <c r="P12" s="9">
-        <v>0.17730496453900699</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="9">
         <v>0</v>
       </c>
       <c r="R12" s="9">
-        <v>2.73556231003039E-2</v>
+        <v>2.3101963666911601E-3</v>
       </c>
       <c r="S12" s="10">
-        <v>0.16514690982776001</v>
+        <v>0.115299800483041</v>
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
-        <v>242</v>
+        <v>73</v>
       </c>
       <c r="C13" s="5">
-        <v>1165</v>
+        <v>7226</v>
       </c>
       <c r="D13" s="9">
-        <v>7.7253218884120095E-2</v>
+        <v>5.0096872405203399E-2</v>
       </c>
       <c r="E13" s="9">
-        <v>0.17424892703862599</v>
+        <v>0.128563520619983</v>
       </c>
       <c r="F13" s="9">
-        <v>2.48927038626609E-2</v>
+        <v>8.2895101024079695E-2</v>
       </c>
       <c r="G13" s="9">
-        <v>4.29184549356223E-3</v>
+        <v>5.88153888735123E-2</v>
       </c>
       <c r="H13" s="9">
-        <v>9.0987124463519295E-2</v>
+        <v>3.8748962081372802E-2</v>
       </c>
       <c r="I13" s="9">
-        <v>0.12789699570815399</v>
+        <v>6.5042900636590004E-2</v>
       </c>
       <c r="J13" s="9">
-        <v>0.190557939914163</v>
+        <v>9.6180459451978895E-2</v>
       </c>
       <c r="K13" s="9">
-        <v>1.71673819742489E-3</v>
+        <v>1.6606698034873999E-3</v>
       </c>
       <c r="L13" s="9">
-        <v>0.15107296137338999</v>
+        <v>0.111264876833656</v>
       </c>
       <c r="M13" s="9">
-        <v>8.5836909871244598E-4</v>
+        <v>1.12095211735399E-2</v>
       </c>
       <c r="N13" s="9">
-        <v>1.5450643776823999E-2</v>
+        <v>0.167174093551065</v>
       </c>
       <c r="O13" s="9">
-        <v>4.2060085836909802E-2</v>
+        <v>1.28701909770274E-2</v>
       </c>
       <c r="P13" s="9">
         <v>0</v>
@@ -3196,54 +3199,54 @@
         <v>0</v>
       </c>
       <c r="R13" s="9">
-        <v>3.1759656652360503E-2</v>
+        <v>6.9748131746471001E-2</v>
       </c>
       <c r="S13" s="10">
-        <v>6.6952789699570803E-2</v>
+        <v>0.10572931082203101</v>
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
-        <v>264</v>
+        <v>343</v>
       </c>
       <c r="C14" s="5">
-        <v>9523</v>
+        <v>407</v>
       </c>
       <c r="D14" s="9">
-        <v>1.0500892575868901E-2</v>
+        <v>4.6683046683046597E-2</v>
       </c>
       <c r="E14" s="9">
-        <v>0.12716580909377201</v>
+        <v>0.14250614250614199</v>
       </c>
       <c r="F14" s="9">
-        <v>4.20035703034757E-3</v>
+        <v>1.7199017199017199E-2</v>
       </c>
       <c r="G14" s="9">
-        <v>5.9855087682453003E-3</v>
+        <v>2.45700245700245E-3</v>
       </c>
       <c r="H14" s="9">
-        <v>2.3942035072981201E-2</v>
+        <v>3.6855036855036799E-2</v>
       </c>
       <c r="I14" s="9">
-        <v>7.5291399768980305E-2</v>
+        <v>8.5995085995085999E-2</v>
       </c>
       <c r="J14" s="9">
-        <v>0.103223774020791</v>
+        <v>7.1253071253071204E-2</v>
       </c>
       <c r="K14" s="9">
-        <v>4.2003570303475701E-4</v>
+        <v>0.22113022113022099</v>
       </c>
       <c r="L14" s="9">
-        <v>0.113934684448178</v>
+        <v>0.174447174447174</v>
       </c>
       <c r="M14" s="9">
-        <v>3.1502677727606799E-4</v>
+        <v>3.9312039312039297E-2</v>
       </c>
       <c r="N14" s="9">
-        <v>0.17515488816549399</v>
+        <v>0.105651105651105</v>
       </c>
       <c r="O14" s="9">
-        <v>0.24225559172529601</v>
+        <v>4.9140049140049102E-2</v>
       </c>
       <c r="P14" s="9">
         <v>0</v>
@@ -3252,54 +3255,54 @@
         <v>0</v>
       </c>
       <c r="R14" s="9">
-        <v>2.3101963666911601E-3</v>
+        <v>7.3710073710073704E-3</v>
       </c>
       <c r="S14" s="10">
-        <v>0.115299800483041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="C15" s="5">
-        <v>1606</v>
+        <v>744</v>
       </c>
       <c r="D15" s="9">
-        <v>4.4209215442092102E-2</v>
+        <v>1.6129032258064498E-2</v>
       </c>
       <c r="E15" s="9">
-        <v>3.1133250311332502E-3</v>
+        <v>0.146505376344086</v>
       </c>
       <c r="F15" s="9">
-        <v>1.2453300124532999E-3</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G15" s="9">
-        <v>0</v>
+        <v>4.9731182795698901E-2</v>
       </c>
       <c r="H15" s="9">
-        <v>0.13200498132004901</v>
+        <v>3.36021505376344E-2</v>
       </c>
       <c r="I15" s="9">
-        <v>8.7173100871730993E-3</v>
+        <v>3.36021505376344E-2</v>
       </c>
       <c r="J15" s="9">
-        <v>0.13885429638854199</v>
+        <v>3.2258064516128997E-2</v>
       </c>
       <c r="K15" s="9">
-        <v>0</v>
+        <v>2.6881720430107499E-3</v>
       </c>
       <c r="L15" s="9">
-        <v>0.231631382316313</v>
+        <v>0.135752688172043</v>
       </c>
       <c r="M15" s="9">
-        <v>9.5890410958904104E-2</v>
+        <v>6.0483870967741903E-2</v>
       </c>
       <c r="N15" s="9">
-        <v>6.2266500622664995E-4</v>
+        <v>0.204301075268817</v>
       </c>
       <c r="O15" s="9">
-        <v>1.86799501867995E-2</v>
+        <v>6.7204301075268801E-3</v>
       </c>
       <c r="P15" s="9">
         <v>0</v>
@@ -3308,54 +3311,54 @@
         <v>0</v>
       </c>
       <c r="R15" s="9">
-        <v>0.123910336239103</v>
+        <v>5.1075268817204297E-2</v>
       </c>
       <c r="S15" s="10">
-        <v>0.201120797011207</v>
+        <v>0.143817204301075</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C16" s="5">
-        <v>2216</v>
+        <v>1165</v>
       </c>
       <c r="D16" s="9">
-        <v>3.4747292418772502E-2</v>
+        <v>7.7253218884120095E-2</v>
       </c>
       <c r="E16" s="9">
-        <v>0.180505415162454</v>
+        <v>0.17424892703862599</v>
       </c>
       <c r="F16" s="9">
-        <v>8.5740072202166E-3</v>
+        <v>2.48927038626609E-2</v>
       </c>
       <c r="G16" s="9">
-        <v>6.7689530685920499E-3</v>
+        <v>4.29184549356223E-3</v>
       </c>
       <c r="H16" s="9">
-        <v>3.2942238267147997E-2</v>
+        <v>9.0987124463519295E-2</v>
       </c>
       <c r="I16" s="9">
-        <v>9.7021660649819499E-2</v>
+        <v>0.12789699570815399</v>
       </c>
       <c r="J16" s="9">
-        <v>9.2057761732851906E-2</v>
+        <v>0.190557939914163</v>
       </c>
       <c r="K16" s="9">
-        <v>0</v>
+        <v>1.71673819742489E-3</v>
       </c>
       <c r="L16" s="9">
-        <v>0.11101083032490899</v>
+        <v>0.15107296137338999</v>
       </c>
       <c r="M16" s="9">
-        <v>0</v>
+        <v>8.5836909871244598E-4</v>
       </c>
       <c r="N16" s="9">
-        <v>0.23465703971119101</v>
+        <v>1.5450643776823999E-2</v>
       </c>
       <c r="O16" s="9">
-        <v>0.19494584837545101</v>
+        <v>4.2060085836909802E-2</v>
       </c>
       <c r="P16" s="9">
         <v>0</v>
@@ -3364,110 +3367,110 @@
         <v>0</v>
       </c>
       <c r="R16" s="9">
-        <v>4.0613718411552299E-3</v>
+        <v>3.1759656652360503E-2</v>
       </c>
       <c r="S16" s="10">
-        <v>2.7075812274368199E-3</v>
+        <v>6.6952789699570803E-2</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
-        <v>300</v>
+        <v>226</v>
       </c>
       <c r="C17" s="5">
-        <v>115</v>
+        <v>2216</v>
       </c>
       <c r="D17" s="9">
-        <v>0</v>
+        <v>3.4747292418772502E-2</v>
       </c>
       <c r="E17" s="9">
-        <v>0</v>
+        <v>0.180505415162454</v>
       </c>
       <c r="F17" s="9">
-        <v>0</v>
+        <v>8.5740072202166E-3</v>
       </c>
       <c r="G17" s="9">
-        <v>0</v>
+        <v>6.7689530685920499E-3</v>
       </c>
       <c r="H17" s="9">
-        <v>0</v>
+        <v>3.2942238267147997E-2</v>
       </c>
       <c r="I17" s="9">
-        <v>0</v>
+        <v>9.7021660649819499E-2</v>
       </c>
       <c r="J17" s="9">
-        <v>0</v>
+        <v>9.2057761732851906E-2</v>
       </c>
       <c r="K17" s="9">
         <v>0</v>
       </c>
       <c r="L17" s="9">
-        <v>0</v>
+        <v>0.11101083032490899</v>
       </c>
       <c r="M17" s="9">
         <v>0</v>
       </c>
       <c r="N17" s="9">
-        <v>0</v>
+        <v>0.23465703971119101</v>
       </c>
       <c r="O17" s="9">
-        <v>0</v>
+        <v>0.19494584837545101</v>
       </c>
       <c r="P17" s="9">
         <v>0</v>
       </c>
-      <c r="Q17" s="12">
-        <v>1</v>
+      <c r="Q17" s="9">
+        <v>0</v>
       </c>
       <c r="R17" s="9">
-        <v>0</v>
+        <v>4.0613718411552299E-3</v>
       </c>
       <c r="S17" s="10">
-        <v>0</v>
+        <v>2.7075812274368199E-3</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="C18" s="5">
-        <v>10918</v>
+        <v>2164</v>
       </c>
       <c r="D18" s="9">
-        <v>4.4696830921414098E-2</v>
+        <v>4.0203327171903801E-2</v>
       </c>
       <c r="E18" s="9">
-        <v>0.11311595530316899</v>
+        <v>0.190388170055452</v>
       </c>
       <c r="F18" s="9">
-        <v>6.6862062648836698E-3</v>
+        <v>0.134011090573012</v>
       </c>
       <c r="G18" s="9">
-        <v>3.0225315991939902E-3</v>
+        <v>7.8096118299445405E-2</v>
       </c>
       <c r="H18" s="9">
-        <v>0.123282652500457</v>
+        <v>1.4325323475046199E-2</v>
       </c>
       <c r="I18" s="9">
-        <v>7.2907125847224696E-2</v>
+        <v>6.3308687615526799E-2</v>
       </c>
       <c r="J18" s="9">
-        <v>0.10249129877266799</v>
+        <v>2.2643253234750398E-2</v>
       </c>
       <c r="K18" s="9">
-        <v>9.1591866642242099E-4</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9">
-        <v>9.9560359040117202E-2</v>
+        <v>0.125693160813308</v>
       </c>
       <c r="M18" s="9">
-        <v>1.5570617329181101E-3</v>
+        <v>5.9611829944547098E-2</v>
       </c>
       <c r="N18" s="9">
-        <v>0.139860780362703</v>
+        <v>0.248613678373382</v>
       </c>
       <c r="O18" s="9">
-        <v>0.20324235207913499</v>
+        <v>4.6210720887245801E-3</v>
       </c>
       <c r="P18" s="9">
         <v>0</v>
@@ -3476,10 +3479,10 @@
         <v>0</v>
       </c>
       <c r="R18" s="9">
-        <v>2.4729803993405299E-3</v>
+        <v>1.8022181146025801E-2</v>
       </c>
       <c r="S18" s="10">
-        <v>8.6187946510349805E-2</v>
+        <v>4.6210720887245802E-4</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
@@ -3540,46 +3543,46 @@
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
-        <v>343</v>
+        <v>40</v>
       </c>
       <c r="C20" s="5">
-        <v>407</v>
+        <v>2832</v>
       </c>
       <c r="D20" s="9">
-        <v>4.6683046683046597E-2</v>
+        <v>5.1906779661016901E-2</v>
       </c>
       <c r="E20" s="9">
-        <v>0.14250614250614199</v>
+        <v>0.23764124293785299</v>
       </c>
       <c r="F20" s="9">
-        <v>1.7199017199017199E-2</v>
+        <v>0.19209039548022599</v>
       </c>
       <c r="G20" s="9">
-        <v>2.45700245700245E-3</v>
+        <v>0.114053672316384</v>
       </c>
       <c r="H20" s="9">
-        <v>3.6855036855036799E-2</v>
+        <v>1.02401129943502E-2</v>
       </c>
       <c r="I20" s="9">
-        <v>8.5995085995085999E-2</v>
+        <v>9.63983050847457E-2</v>
       </c>
       <c r="J20" s="9">
-        <v>7.1253071253071204E-2</v>
+        <v>6.0028248587570597E-3</v>
       </c>
       <c r="K20" s="9">
-        <v>0.22113022113022099</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9">
-        <v>0.174447174447174</v>
+        <v>2.4717514124293701E-3</v>
       </c>
       <c r="M20" s="9">
-        <v>3.9312039312039297E-2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>0.105651105651105</v>
+        <v>0.27048022598869997</v>
       </c>
       <c r="O20" s="9">
-        <v>4.9140049140049102E-2</v>
+        <v>6.70903954802259E-3</v>
       </c>
       <c r="P20" s="9">
         <v>0</v>
@@ -3588,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="R20" s="9">
-        <v>7.3710073710073704E-3</v>
+        <v>1.20056497175141E-2</v>
       </c>
       <c r="S20" s="10">
         <v>0</v>
@@ -3660,6 +3663,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:P20 R3:S20">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3676,16 +3687,6 @@
         <cfvo type="max"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:P20 R3:S20">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
